--- a/data/OkFileDefinitions/TJXNA_PreticketLayout.xlsx
+++ b/data/OkFileDefinitions/TJXNA_PreticketLayout.xlsx
@@ -481,7 +481,7 @@
     <t xml:space="preserve">fact3                    </t>
   </si>
   <si>
-    <t xml:space="preserve">00100142103239702      NXXXXXXXXXX          001800N00099900220007194339000454218                                                                                                          </t>
+    <t xml:space="preserve">00100142103239702      NXXXXXXXXXX          001800N00099900220007194339000454218                                                                                                          VENDORST</t>
   </si>
 </sst>
 </file>
@@ -8085,7 +8085,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K28"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -9015,6 +9015,57 @@
         <v xml:space="preserve">                    </v>
       </c>
     </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="2">
+        <v>41</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Lane</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>field174</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>vendor_style</t>
+        </is>
+      </c>
+      <c r="E29" s="2">
+        <v>8</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>vendor_style</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>char</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Pre-Ticket</t>
+        </is>
+      </c>
+      <c r="J29" s="2">
+        <v>187</v>
+      </c>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>VENDORST</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
